--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
   <si>
     <t>Profile</t>
   </si>
@@ -69,6 +69,24 @@
   </si>
   <si>
     <t>optional</t>
+  </si>
+  <si>
+    <t>jp-observation-endoscopy</t>
+  </si>
+  <si>
+    <t>JP Core Observation Endoscopy Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP7796-8</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS (preferred)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ, stringĵ</t>
   </si>
   <si>
     <t>jp-observation-labresult</t>
@@ -298,7 +316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -426,10 +444,10 @@
         <v>28</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -443,28 +461,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -478,28 +496,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -528,13 +546,13 @@
         <v>42</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -548,28 +566,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>24</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -583,13 +601,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s" s="2">
         <v>14</v>
@@ -598,21 +616,56 @@
         <v>14</v>
       </c>
       <c r="F9" t="s" s="2">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I9" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s" s="2">
+      <c r="I10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K10" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -149,7 +149,7 @@
     <t>dateTime</t>
   </si>
   <si>
-    <t>string</t>
+    <t>stringĵ</t>
   </si>
   <si>
     <t>jp-observation-radiology-impression</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
   <si>
     <t>Profile</t>
   </si>
@@ -71,6 +71,21 @@
     <t>optional</t>
   </si>
   <si>
+    <t>jp-observation-electrocardiogram</t>
+  </si>
+  <si>
+    <t>JP Core Observation Electrocardiogram Profile</t>
+  </si>
+  <si>
+    <t>null#11524-6</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
     <t>jp-observation-endoscopy</t>
   </si>
   <si>
@@ -141,9 +156,6 @@
   </si>
   <si>
     <t>null#18782-3</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -316,7 +328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -397,13 +409,13 @@
         <v>20</v>
       </c>
       <c r="C3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>21</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>22</v>
@@ -412,7 +424,7 @@
         <v>23</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>18</v>
@@ -426,28 +438,28 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>25</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="C4" t="s" s="2">
+      <c r="D4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s" s="2">
+      <c r="G4" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="G4" t="s" s="2">
+      <c r="H4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="H4" t="s" s="2">
-        <v>30</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -461,28 +473,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="C5" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="C5" t="s" s="2">
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F5" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s" s="2">
+      <c r="G5" t="s" s="2">
         <v>34</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>16</v>
-      </c>
       <c r="H5" t="s" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -496,19 +508,19 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>39</v>
@@ -517,7 +529,7 @@
         <v>16</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -537,22 +549,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -566,28 +578,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="C8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
+      <c r="F8" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="F8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>44</v>
-      </c>
       <c r="H8" t="s" s="2">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -601,28 +613,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>30</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -657,15 +669,50 @@
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I10" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K10" t="s" s="2">
+      <c r="I11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
   <si>
     <t>Profile</t>
   </si>
@@ -80,82 +80,85 @@
     <t>null#11524-6</t>
   </si>
   <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS (preferred)</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing, instant</t>
+  </si>
+  <si>
+    <t>jp-observation-endoscopy</t>
+  </si>
+  <si>
+    <t>JP Core Observation Endoscopy Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP7796-8</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS (preferred)</t>
+  </si>
+  <si>
+    <t>dateTimeĵ, Periodĵ</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ, stringĵ</t>
+  </si>
+  <si>
+    <t>jp-observation-labresult</t>
+  </si>
+  <si>
+    <t>JP Core Observation LabResult Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#laboratory</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (preferred)</t>
+  </si>
+  <si>
+    <t>dateTime, Period, Timing</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string</t>
+  </si>
+  <si>
+    <t>jp-observation-microbiology</t>
+  </si>
+  <si>
+    <t>JP Core Observation Microbiology Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (required)</t>
+  </si>
+  <si>
+    <t>jp-observation-physicalexam</t>
+  </si>
+  <si>
+    <t>JP Core Observation PhysicalExam Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#exam</t>
+  </si>
+  <si>
+    <t>null#physical-findings</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
+  </si>
+  <si>
+    <t>jp-observation-radiology-findings</t>
+  </si>
+  <si>
+    <t>JP Core Observation Radiology Findings Profile</t>
+  </si>
+  <si>
+    <t>null#18782-3</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
-    <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>jp-observation-endoscopy</t>
-  </si>
-  <si>
-    <t>JP Core Observation Endoscopy Profile</t>
-  </si>
-  <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP7796-8</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS (preferred)</t>
-  </si>
-  <si>
-    <t>dateTimeĵ, Periodĵ</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ, stringĵ</t>
-  </si>
-  <si>
-    <t>jp-observation-labresult</t>
-  </si>
-  <si>
-    <t>JP Core Observation LabResult Profile</t>
-  </si>
-  <si>
-    <t>JP Core Simple Observation Category CodeSystem#laboratory</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (preferred)</t>
-  </si>
-  <si>
-    <t>dateTime, Period, Timing</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string</t>
-  </si>
-  <si>
-    <t>jp-observation-microbiology</t>
-  </si>
-  <si>
-    <t>JP Core Observation Microbiology Profile</t>
-  </si>
-  <si>
-    <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (required)</t>
-  </si>
-  <si>
-    <t>jp-observation-physicalexam</t>
-  </si>
-  <si>
-    <t>JP Core Observation PhysicalExam Profile</t>
-  </si>
-  <si>
-    <t>JP Core Simple Observation Category CodeSystem#exam</t>
-  </si>
-  <si>
-    <t>null#physical-findings</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
-  </si>
-  <si>
-    <t>jp-observation-radiology-findings</t>
-  </si>
-  <si>
-    <t>JP Core Observation Radiology Findings Profile</t>
-  </si>
-  <si>
-    <t>null#18782-3</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -593,13 +596,13 @@
         <v>47</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -613,28 +616,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>50</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -648,13 +651,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
@@ -663,7 +666,7 @@
         <v>14</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -683,13 +686,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
@@ -698,7 +701,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
   <si>
     <t>Profile</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>JP Core Observation Electrocardiogram Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure</t>
   </si>
   <si>
     <t>null#11524-6</t>
@@ -412,19 +415,19 @@
         <v>20</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>17</v>
@@ -441,13 +444,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>14</v>
@@ -456,13 +459,13 @@
         <v>14</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -476,13 +479,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
@@ -491,13 +494,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -511,13 +514,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
@@ -526,13 +529,13 @@
         <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -546,22 +549,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>16</v>
@@ -581,10 +584,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -593,16 +596,16 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -616,28 +619,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>50</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -651,13 +654,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
@@ -666,13 +669,13 @@
         <v>14</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -686,13 +689,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
@@ -701,7 +704,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
   <si>
     <t>Profile</t>
   </si>
@@ -77,7 +77,10 @@
     <t>JP Core Observation Electrocardiogram Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure</t>
+    <t>null#procedure</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS (required)</t>
   </si>
   <si>
     <t>null#11524-6</t>
@@ -418,16 +421,16 @@
         <v>21</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>17</v>
@@ -444,13 +447,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s" s="2">
         <v>14</v>
@@ -459,13 +462,13 @@
         <v>14</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -479,13 +482,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
@@ -494,13 +497,13 @@
         <v>14</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -514,13 +517,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
@@ -529,13 +532,13 @@
         <v>14</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -549,22 +552,22 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>16</v>
@@ -584,10 +587,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -596,16 +599,16 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -619,28 +622,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -654,13 +657,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>14</v>
@@ -669,13 +672,13 @@
         <v>14</v>
       </c>
       <c r="F10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -689,13 +692,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
@@ -704,7 +707,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
   <si>
     <t>Profile</t>
   </si>
@@ -80,13 +80,13 @@
     <t>null#procedure</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
     <t>null#11524-6</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS (preferred)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>null#18782-3</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -602,13 +599,13 @@
         <v>49</v>
       </c>
       <c r="F8" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -622,28 +619,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>55</v>
-      </c>
       <c r="F9" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="G9" t="s" s="2">
+      <c r="H9" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>52</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -657,22 +654,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>57</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>58</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>59</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -692,22 +689,22 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F11" t="s" s="2">
         <v>62</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>63</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -71,6 +71,45 @@
     <t>optional</t>
   </si>
   <si>
+    <t>jp-observation-dentaloral-missingtoothcondition</t>
+  </si>
+  <si>
+    <t>JP Core Observation DentalOral Missing Tooth Condition Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#MissingToothCondition</t>
+  </si>
+  <si>
+    <t>null#54570-7</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
+    <t>jp-observation-dentaloral-toothexistence</t>
+  </si>
+  <si>
+    <t>JP Core Observation DentalOral Tooth Existence Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
+  </si>
+  <si>
+    <t>jp-observation-dentaloral-toothtreatmentcondition</t>
+  </si>
+  <si>
+    <t>JP Core Observation DentalOral Tooth Treatment Condition Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
+  </si>
+  <si>
     <t>jp-observation-electrocardiogram</t>
   </si>
   <si>
@@ -83,10 +122,7 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
-    <t>null#11524-6</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>LOINC#11524-6</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -162,9 +198,6 @@
   </si>
   <si>
     <t>null#18782-3</t>
-  </si>
-  <si>
-    <t>dateTime</t>
   </si>
   <si>
     <t>stringĵ</t>
@@ -334,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -418,19 +451,19 @@
         <v>21</v>
       </c>
       <c r="D3" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="E3" t="s" s="2">
+      <c r="F3" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="F3" t="s" s="2">
+      <c r="G3" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="G3" t="s" s="2">
+      <c r="H3" t="s" s="2">
         <v>25</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>18</v>
@@ -456,16 +489,16 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -479,28 +512,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s" s="2">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -514,28 +547,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -549,28 +582,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="G7" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="H7" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>17</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -584,28 +617,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>48</v>
       </c>
-      <c r="C8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>51</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -619,28 +652,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>52</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="C9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>24</v>
-      </c>
       <c r="G9" t="s" s="2">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -654,19 +687,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
-        <v>14</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>58</v>
@@ -675,7 +708,7 @@
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -695,30 +728,135 @@
         <v>60</v>
       </c>
       <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F11" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>62</v>
       </c>
-      <c r="G11" t="s" s="2">
+      <c r="I11" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="I12" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K12" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>16</v>
       </c>
-      <c r="H11" t="s" s="2">
+      <c r="H13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="I13" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H14" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I11" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K11" t="s" s="2">
+      <c r="I14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -122,7 +122,7 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
-    <t>LOINC#11524-6</t>
+    <t>null#11524-6</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>37</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -122,7 +122,7 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
   </si>
   <si>
-    <t>null#11524-6</t>
+    <t>LOINC#11524-6</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -562,7 +562,7 @@
         <v>36</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>37</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
   <si>
     <t>Profile</t>
   </si>
@@ -116,10 +116,7 @@
     <t>JP Core Observation Electrocardiogram Profile</t>
   </si>
   <si>
-    <t>null#procedure</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS (example)</t>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#11524-6</t>
   </si>
   <si>
     <t>LOINC#11524-6</t>
@@ -556,16 +553,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E6" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="E6" t="s" s="2">
+      <c r="F6" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="F6" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>17</v>
@@ -582,28 +579,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F7" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s" s="2">
+      <c r="G7" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="G7" t="s" s="2">
+      <c r="H7" t="s" s="2">
         <v>42</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>43</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -617,28 +614,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="C8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="G8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>48</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>49</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -652,28 +649,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="C9" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="C9" t="s" s="2">
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>53</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -687,22 +684,22 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="C10" t="s" s="2">
+      <c r="D10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="D10" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s" s="2">
+      <c r="F10" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
@@ -722,19 +719,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>60</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
-        <v>61</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -743,7 +740,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -757,19 +754,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E12" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E12" t="s" s="2">
-        <v>65</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -778,7 +775,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -792,28 +789,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="C13" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="C13" t="s" s="2">
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -827,22 +824,22 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>70</v>
       </c>
-      <c r="B14" t="s" s="2">
+      <c r="C14" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="C14" t="s" s="2">
+      <c r="D14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F14" t="s" s="2">
         <v>72</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s" s="2">
-        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -164,7 +164,7 @@
     <t>jp-observation-microbiology</t>
   </si>
   <si>
-    <t>JP Core Observation Microbiology Profile</t>
+    <t>JP Core Observationsecond Profile</t>
   </si>
   <si>
     <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -164,7 +164,7 @@
     <t>jp-observation-microbiology</t>
   </si>
   <si>
-    <t>JP Core Observationsecond Profile</t>
+    <t>JP Core Observation Microbiology Profile</t>
   </si>
   <si>
     <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -77,7 +77,7 @@
     <t>JP Core Observation DentalOral Missing Tooth Condition Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#MissingToothCondition</t>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-03</t>
   </si>
   <si>
     <t>null#54570-7</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
   <si>
     <t>Profile</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>JP Core Observation Radiology Findings Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#imaging</t>
   </si>
   <si>
     <t>null#18782-3</t>
@@ -725,13 +728,13 @@
         <v>59</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>23</v>
@@ -740,7 +743,7 @@
         <v>24</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -754,19 +757,19 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>23</v>
@@ -775,7 +778,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -789,13 +792,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>14</v>
@@ -804,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>16</v>
@@ -824,13 +827,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>14</v>
@@ -839,7 +842,7 @@
         <v>14</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>16</v>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -140,7 +140,7 @@
     <t>dateTimeĵ, Periodĵ</t>
   </si>
   <si>
-    <t>CodeableConceptĵ, stringĵ</t>
+    <t>CodeableConceptĵ</t>
   </si>
   <si>
     <t>jp-observation-labresult</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="78">
   <si>
     <t>Profile</t>
   </si>
@@ -71,34 +71,46 @@
     <t>optional</t>
   </si>
   <si>
+    <t>jp-observation-dentaloral-ecs</t>
+  </si>
+  <si>
+    <t>JP Core Observation DentalOral eCS Profile</t>
+  </si>
+  <si>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-04</t>
+  </si>
+  <si>
+    <t>null#57133-1</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>CodeableConcept</t>
+  </si>
+  <si>
     <t>jp-observation-dentaloral-missingtoothcondition</t>
   </si>
   <si>
     <t>JP Core Observation DentalOral Missing Tooth Condition Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-03</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-03</t>
   </si>
   <si>
     <t>null#54570-7</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>CodeableConcept</t>
-  </si>
-  <si>
     <t>jp-observation-dentaloral-toothexistence</t>
   </si>
   <si>
     <t>JP Core Observation DentalOral Tooth Existence Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-01</t>
   </si>
   <si>
     <t>jp-observation-dentaloral-toothtreatmentcondition</t>
@@ -107,7 +119,7 @@
     <t>JP Core Observation DentalOral Tooth Treatment Condition Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
+    <t>JP Core Simple Observation Category CodeSystem#exam, LOINC#LP89803-8, JP Core ObservationDentalCategory CodeSystem#DO-1-02</t>
   </si>
   <si>
     <t>jp-observation-electrocardiogram</t>
@@ -367,7 +379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -489,7 +501,7 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s" s="2">
         <v>23</v>
@@ -512,19 +524,19 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>22</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>23</v>
@@ -547,28 +559,28 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -582,28 +594,28 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
         <v>38</v>
       </c>
-      <c r="C7" t="s" s="2">
+      <c r="D7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>39</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>14</v>
-      </c>
       <c r="F7" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="G7" t="s" s="2">
-        <v>41</v>
-      </c>
       <c r="H7" t="s" s="2">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -617,28 +629,28 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="C8" t="s" s="2">
         <v>43</v>
       </c>
-      <c r="B8" t="s" s="2">
+      <c r="D8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="C8" t="s" s="2">
+      <c r="G8" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s" s="2">
+      <c r="H8" t="s" s="2">
         <v>46</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -652,28 +664,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="D9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F9" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C9" t="s" s="2">
+      <c r="G9" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="D9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s" s="2">
+      <c r="H9" t="s" s="2">
         <v>52</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -699,16 +711,16 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" t="s" s="2">
         <v>56</v>
-      </c>
-      <c r="F10" t="s" s="2">
-        <v>57</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -722,28 +734,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>58</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="C11" t="s" s="2">
+      <c r="D11" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="D11" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s" s="2">
+      <c r="F11" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="F11" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="G11" t="s" s="2">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -757,13 +769,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
         <v>64</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>14</v>
@@ -778,7 +790,7 @@
         <v>24</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -792,28 +804,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s" s="2">
         <v>66</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>48</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -848,15 +860,50 @@
         <v>16</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="I14" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J14" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K14" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H15" t="s" s="2">
         <v>17</v>
       </c>
-      <c r="I14" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K14" t="s" s="2">
+      <c r="I15" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -83,7 +83,7 @@
     <t>null#57133-1</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
     <t>dateTime</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -53,7 +53,7 @@
     <t>JP Core Observation BodyMeasurement Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#body-measurement</t>
+    <t>JP Core Simple Observation Category CodeSystem#body-measurement, JP Core Observation BodyMeasurement Category CodeSystem#null</t>
   </si>
   <si>
     <t/>
@@ -128,7 +128,7 @@
     <t>JP Core Observation Electrocardiogram Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#11524-6</t>
+    <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#11524-6, JP Core Observation Electrocardiogram Extra Category CodeSystem#null</t>
   </si>
   <si>
     <t>LOINC#11524-6</t>
@@ -242,7 +242,7 @@
     <t>JP Core Observation VitalSigns Profile</t>
   </si>
   <si>
-    <t>JP Core Simple Observation Category CodeSystem#vital-signs</t>
+    <t>JP Core Simple Observation Category CodeSystem#vital-signs, JP Core Observation VitalSigns Category CodeSystem#null</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS (preferred)</t>

--- a/jpcore-r4/develop/observations-summary.xlsx
+++ b/jpcore-r4/develop/observations-summary.xlsx
@@ -197,7 +197,7 @@
     <t>null#physical-findings</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (preferred)</t>
   </si>
   <si>
     <t>jp-observation-radiology-findings</t>
